--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/TEXAS_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/TEXAS_2024.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C230">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C278">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C444">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C584">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C948">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C950">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C951">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>Santo Domingo Ingeni</t>
+          <t>Santo Domingo Ingenio</t>
         </is>
       </c>
       <c r="C1245">
